--- a/HA/home/таблица.xlsx
+++ b/HA/home/таблица.xlsx
@@ -5,16 +5,16 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\---__HA_files\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\_GitHub\python_prj\HA\home\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E161B89-385A-4F5D-871E-85AE05633532}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D226A90-281A-4801-B9F5-CCC76A2061E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Лист1" sheetId="1" r:id="rId1"/>
-    <sheet name="Лист2" sheetId="2" r:id="rId2"/>
+    <sheet name="ModBus" sheetId="1" r:id="rId1"/>
+    <sheet name="Zigbee" sheetId="2" r:id="rId2"/>
     <sheet name="Лист3" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="145621"/>
@@ -649,7 +649,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -694,13 +694,21 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -709,15 +717,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -1022,6 +1021,9 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr>
+    <tabColor rgb="FF92D050"/>
+  </sheetPr>
   <dimension ref="A1:E111"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -1032,19 +1034,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="18" x14ac:dyDescent="0.35">
-      <c r="A1" s="28" t="s">
+      <c r="A1" s="26" t="s">
         <v>65</v>
       </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
     </row>
     <row r="2" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="3" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="27"/>
+      <c r="B3" s="25"/>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
       <c r="E3" s="3"/>
@@ -1148,7 +1150,7 @@
       <c r="A13" s="24" t="s">
         <v>5</v>
       </c>
-      <c r="B13" s="27"/>
+      <c r="B13" s="25"/>
       <c r="C13" s="2"/>
       <c r="D13" s="2"/>
       <c r="E13" s="3"/>
@@ -1161,7 +1163,7 @@
         <v>144</v>
       </c>
       <c r="C14" s="2"/>
-      <c r="D14" s="30" t="s">
+      <c r="D14" s="23" t="s">
         <v>145</v>
       </c>
       <c r="E14" s="3"/>
@@ -1218,7 +1220,7 @@
         <v>143</v>
       </c>
       <c r="C19" s="2"/>
-      <c r="D19" s="30" t="s">
+      <c r="D19" s="23" t="s">
         <v>146</v>
       </c>
       <c r="E19" s="3"/>
@@ -1256,7 +1258,7 @@
       <c r="A23" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="B23" s="27"/>
+      <c r="B23" s="25"/>
       <c r="C23" s="2"/>
       <c r="D23" s="2"/>
       <c r="E23" s="3"/>
@@ -1360,7 +1362,7 @@
       <c r="A33" s="24" t="s">
         <v>16</v>
       </c>
-      <c r="B33" s="27"/>
+      <c r="B33" s="25"/>
       <c r="C33" s="2"/>
       <c r="D33" s="2"/>
       <c r="E33" s="3"/>
@@ -1462,7 +1464,7 @@
       <c r="A43" s="24" t="s">
         <v>17</v>
       </c>
-      <c r="B43" s="27"/>
+      <c r="B43" s="25"/>
       <c r="C43" s="2"/>
       <c r="D43" s="2"/>
       <c r="E43" s="3"/>
@@ -1571,7 +1573,7 @@
       <c r="A54" s="24" t="s">
         <v>19</v>
       </c>
-      <c r="B54" s="27"/>
+      <c r="B54" s="25"/>
       <c r="C54" s="2"/>
       <c r="D54" s="2"/>
       <c r="E54" s="3"/>
@@ -1674,7 +1676,7 @@
       <c r="A64" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="B64" s="25"/>
+      <c r="B64" s="29"/>
       <c r="C64" s="2"/>
       <c r="D64" s="2"/>
       <c r="E64" s="3"/>
@@ -1703,11 +1705,11 @@
       <c r="A67" s="12">
         <v>3</v>
       </c>
-      <c r="B67" s="31" t="s">
+      <c r="B67" s="4" t="s">
         <v>23</v>
       </c>
       <c r="C67" s="2"/>
-      <c r="D67" s="29" t="s">
+      <c r="D67" s="22" t="s">
         <v>147</v>
       </c>
       <c r="E67" s="3"/>
@@ -1778,7 +1780,7 @@
       <c r="A74" s="24" t="s">
         <v>24</v>
       </c>
-      <c r="B74" s="25"/>
+      <c r="B74" s="29"/>
       <c r="C74" s="2"/>
       <c r="D74" s="2"/>
       <c r="E74" s="3"/>
@@ -1873,10 +1875,10 @@
       <c r="E83" s="3"/>
     </row>
     <row r="84" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A84" s="26" t="s">
+      <c r="A84" s="30" t="s">
         <v>0</v>
       </c>
-      <c r="B84" s="27"/>
+      <c r="B84" s="25"/>
       <c r="C84" s="2"/>
       <c r="D84" s="2"/>
       <c r="E84" s="3"/>
@@ -1977,10 +1979,10 @@
       <c r="E93" s="3"/>
     </row>
     <row r="94" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A94" s="26" t="s">
+      <c r="A94" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="B94" s="27"/>
+      <c r="B94" s="25"/>
       <c r="C94" s="2"/>
       <c r="D94" s="2"/>
       <c r="E94" s="3"/>
@@ -2081,10 +2083,10 @@
       <c r="E103" s="3"/>
     </row>
     <row r="104" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A104" s="22" t="s">
+      <c r="A104" s="27" t="s">
         <v>57</v>
       </c>
-      <c r="B104" s="23"/>
+      <c r="B104" s="28"/>
       <c r="C104" s="2"/>
       <c r="D104" s="2"/>
       <c r="E104" s="3"/>
@@ -2168,6 +2170,11 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="A104:B104"/>
+    <mergeCell ref="A64:B64"/>
+    <mergeCell ref="A74:B74"/>
+    <mergeCell ref="A84:B84"/>
+    <mergeCell ref="A94:B94"/>
     <mergeCell ref="A54:B54"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A3:B3"/>
@@ -2175,11 +2182,6 @@
     <mergeCell ref="A23:B23"/>
     <mergeCell ref="A33:B33"/>
     <mergeCell ref="A43:B43"/>
-    <mergeCell ref="A104:B104"/>
-    <mergeCell ref="A64:B64"/>
-    <mergeCell ref="A74:B74"/>
-    <mergeCell ref="A84:B84"/>
-    <mergeCell ref="A94:B94"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -2188,6 +2190,9 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <sheetPr>
+    <tabColor rgb="FFFFFF00"/>
+  </sheetPr>
   <dimension ref="A2:A53"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>

--- a/HA/home/таблица.xlsx
+++ b/HA/home/таблица.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\_GitHub\python_prj\HA\home\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD415C1D-FC7D-44D1-9FD0-B4A00FCF1586}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65D53054-29CB-4686-8896-B92BFA1B18DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="154">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="155">
   <si>
     <t>доступ из локальной сети (только дома)    http://homeassistant.local:8123/</t>
   </si>
@@ -489,6 +489,9 @@
   </si>
   <si>
     <t>#</t>
+  </si>
+  <si>
+    <t>Электрощитовая - свет</t>
   </si>
 </sst>
 </file>
@@ -563,7 +566,7 @@
       <charset val="204"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -597,6 +600,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor rgb="FF993300"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
         <bgColor rgb="FF993300"/>
       </patternFill>
     </fill>
@@ -703,16 +712,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -743,9 +749,6 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -773,12 +776,6 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -793,6 +790,21 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -1071,1149 +1083,1156 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="18" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="34" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
+      <c r="B1" s="34"/>
+      <c r="C1" s="34"/>
+      <c r="D1" s="34"/>
     </row>
     <row r="3" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A3" s="17" t="s">
+      <c r="A3" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="17"/>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4"/>
-      <c r="E3" s="5"/>
+      <c r="B3" s="33"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="4"/>
     </row>
     <row r="4" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A4" s="18">
+      <c r="A4" s="16">
         <v>1</v>
       </c>
-      <c r="B4" s="19" t="s">
+      <c r="B4" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="4"/>
-      <c r="D4" s="6" t="s">
+      <c r="C4" s="3"/>
+      <c r="D4" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E4" s="5"/>
+      <c r="E4" s="4"/>
     </row>
     <row r="5" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A5" s="18">
+      <c r="A5" s="16">
         <v>2</v>
       </c>
-      <c r="B5" s="19" t="s">
+      <c r="B5" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="4"/>
-      <c r="D5" s="7" t="s">
+      <c r="C5" s="3"/>
+      <c r="D5" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="E5" s="5"/>
+      <c r="E5" s="4"/>
     </row>
     <row r="6" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A6" s="18">
+      <c r="A6" s="16">
         <v>3</v>
       </c>
-      <c r="B6" s="19" t="s">
+      <c r="B6" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="4"/>
-      <c r="D6" s="4"/>
-      <c r="E6" s="5"/>
+      <c r="C6" s="3"/>
+      <c r="D6" s="3"/>
+      <c r="E6" s="4"/>
     </row>
     <row r="7" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A7" s="18">
+      <c r="A7" s="16">
         <v>4</v>
       </c>
-      <c r="B7" s="19" t="s">
+      <c r="B7" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="4"/>
-      <c r="D7" s="4"/>
-      <c r="E7" s="5"/>
+      <c r="C7" s="3"/>
+      <c r="D7" s="3"/>
+      <c r="E7" s="4"/>
     </row>
     <row r="8" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A8" s="18">
+      <c r="A8" s="16">
         <v>5</v>
       </c>
-      <c r="B8" s="19" t="s">
+      <c r="B8" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="C8" s="4"/>
-      <c r="D8" s="4"/>
-      <c r="E8" s="5"/>
+      <c r="C8" s="3"/>
+      <c r="D8" s="3"/>
+      <c r="E8" s="4"/>
     </row>
     <row r="9" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A9" s="18">
+      <c r="A9" s="16">
         <v>6</v>
       </c>
-      <c r="B9" s="19" t="s">
+      <c r="B9" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="4"/>
-      <c r="D9" s="4"/>
-      <c r="E9" s="5"/>
+      <c r="C9" s="3"/>
+      <c r="D9" s="3"/>
+      <c r="E9" s="4"/>
     </row>
     <row r="10" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A10" s="18">
+      <c r="A10" s="16">
         <v>7</v>
       </c>
-      <c r="B10" s="19" t="s">
+      <c r="B10" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="C10" s="4"/>
-      <c r="D10" s="4"/>
-      <c r="E10" s="5"/>
+      <c r="C10" s="3"/>
+      <c r="D10" s="3"/>
+      <c r="E10" s="4"/>
     </row>
     <row r="11" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A11" s="20">
+      <c r="A11" s="18">
         <v>8</v>
       </c>
-      <c r="B11" s="21" t="s">
+      <c r="B11" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="C11" s="4"/>
-      <c r="D11" s="4"/>
-      <c r="E11" s="5"/>
+      <c r="C11" s="3"/>
+      <c r="D11" s="3"/>
+      <c r="E11" s="4"/>
     </row>
     <row r="12" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A12" s="22"/>
-      <c r="B12" s="22"/>
-      <c r="C12" s="4"/>
-      <c r="D12" s="4"/>
-      <c r="E12" s="5"/>
+      <c r="A12" s="20"/>
+      <c r="B12" s="20"/>
+      <c r="C12" s="3"/>
+      <c r="D12" s="3"/>
+      <c r="E12" s="4"/>
     </row>
     <row r="13" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A13" s="17" t="s">
+      <c r="A13" s="33" t="s">
         <v>12</v>
       </c>
-      <c r="B13" s="17"/>
-      <c r="C13" s="4"/>
-      <c r="D13" s="4"/>
-      <c r="E13" s="5"/>
+      <c r="B13" s="33"/>
+      <c r="C13" s="3"/>
+      <c r="D13" s="3"/>
+      <c r="E13" s="4"/>
     </row>
     <row r="14" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A14" s="18">
+      <c r="A14" s="16">
         <v>1</v>
       </c>
-      <c r="B14" s="19" t="s">
+      <c r="B14" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="C14" s="4"/>
-      <c r="D14" s="33" t="s">
+      <c r="C14" s="3"/>
+      <c r="D14" s="29" t="s">
         <v>14</v>
       </c>
-      <c r="E14" s="5"/>
+      <c r="E14" s="4"/>
     </row>
     <row r="15" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A15" s="18">
+      <c r="A15" s="16">
         <v>2</v>
       </c>
-      <c r="B15" s="19" t="s">
+      <c r="B15" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="C15" s="4"/>
-      <c r="D15" s="4"/>
-      <c r="E15" s="5"/>
+      <c r="C15" s="3"/>
+      <c r="D15" s="3"/>
+      <c r="E15" s="4"/>
     </row>
     <row r="16" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A16" s="18">
+      <c r="A16" s="16">
         <v>3</v>
       </c>
-      <c r="B16" s="19" t="s">
+      <c r="B16" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="C16" s="4"/>
-      <c r="D16" s="4"/>
-      <c r="E16" s="5"/>
+      <c r="C16" s="3"/>
+      <c r="D16" s="3"/>
+      <c r="E16" s="4"/>
     </row>
     <row r="17" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A17" s="18">
+      <c r="A17" s="16">
         <v>4</v>
       </c>
-      <c r="B17" s="19" t="s">
+      <c r="B17" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="C17" s="4"/>
-      <c r="D17" s="4"/>
-      <c r="E17" s="5"/>
+      <c r="C17" s="3"/>
+      <c r="D17" s="3"/>
+      <c r="E17" s="4"/>
     </row>
     <row r="18" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A18" s="18">
+      <c r="A18" s="16">
         <v>5</v>
       </c>
-      <c r="B18" s="19" t="s">
+      <c r="B18" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="C18" s="4"/>
-      <c r="D18" s="4"/>
-      <c r="E18" s="5"/>
+      <c r="C18" s="3"/>
+      <c r="D18" s="3"/>
+      <c r="E18" s="4"/>
     </row>
     <row r="19" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A19" s="18">
+      <c r="A19" s="16">
         <v>6</v>
       </c>
-      <c r="B19" s="19" t="s">
+      <c r="B19" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="C19" s="4"/>
-      <c r="D19" s="33" t="s">
+      <c r="C19" s="3"/>
+      <c r="D19" s="29" t="s">
         <v>20</v>
       </c>
-      <c r="E19" s="5"/>
+      <c r="E19" s="4"/>
     </row>
     <row r="20" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A20" s="18">
+      <c r="A20" s="16">
         <v>7</v>
       </c>
-      <c r="B20" s="19" t="s">
+      <c r="B20" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="C20" s="4"/>
-      <c r="D20" s="4"/>
-      <c r="E20" s="5"/>
+      <c r="C20" s="3"/>
+      <c r="D20" s="3"/>
+      <c r="E20" s="4"/>
     </row>
     <row r="21" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A21" s="20">
+      <c r="A21" s="18">
         <v>8</v>
       </c>
-      <c r="B21" s="21" t="s">
+      <c r="B21" s="19" t="s">
         <v>22</v>
       </c>
-      <c r="C21" s="4"/>
-      <c r="D21" s="4"/>
-      <c r="E21" s="5"/>
+      <c r="C21" s="3"/>
+      <c r="D21" s="3"/>
+      <c r="E21" s="4"/>
     </row>
     <row r="22" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A22" s="22"/>
-      <c r="B22" s="22"/>
-      <c r="C22" s="4"/>
-      <c r="D22" s="4"/>
-      <c r="E22" s="5"/>
+      <c r="A22" s="20"/>
+      <c r="B22" s="20"/>
+      <c r="C22" s="3"/>
+      <c r="D22" s="3"/>
+      <c r="E22" s="4"/>
     </row>
     <row r="23" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A23" s="17" t="s">
+      <c r="A23" s="33" t="s">
         <v>23</v>
       </c>
-      <c r="B23" s="17"/>
-      <c r="C23" s="4"/>
-      <c r="D23" s="4"/>
-      <c r="E23" s="5"/>
+      <c r="B23" s="33"/>
+      <c r="C23" s="3"/>
+      <c r="D23" s="3"/>
+      <c r="E23" s="4"/>
     </row>
     <row r="24" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A24" s="18">
+      <c r="A24" s="16">
         <v>1</v>
       </c>
-      <c r="B24" s="19" t="s">
+      <c r="B24" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="C24" s="4"/>
-      <c r="D24" s="4"/>
-      <c r="E24" s="5"/>
+      <c r="C24" s="3"/>
+      <c r="D24" s="3"/>
+      <c r="E24" s="4"/>
     </row>
     <row r="25" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A25" s="18">
+      <c r="A25" s="16">
         <v>2</v>
       </c>
-      <c r="B25" s="19" t="s">
+      <c r="B25" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="C25" s="4"/>
-      <c r="D25" s="4"/>
-      <c r="E25" s="5"/>
+      <c r="C25" s="3"/>
+      <c r="D25" s="3"/>
+      <c r="E25" s="4"/>
     </row>
     <row r="26" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A26" s="18">
+      <c r="A26" s="16">
         <v>3</v>
       </c>
-      <c r="B26" s="19" t="s">
+      <c r="B26" s="17" t="s">
         <v>26</v>
       </c>
-      <c r="C26" s="4"/>
-      <c r="D26" s="4"/>
-      <c r="E26" s="5"/>
+      <c r="C26" s="3"/>
+      <c r="D26" s="3"/>
+      <c r="E26" s="4"/>
     </row>
     <row r="27" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A27" s="18">
+      <c r="A27" s="16">
         <v>4</v>
       </c>
-      <c r="B27" s="19" t="s">
+      <c r="B27" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="C27" s="4"/>
-      <c r="D27" s="4"/>
-      <c r="E27" s="5"/>
+      <c r="C27" s="3"/>
+      <c r="D27" s="3"/>
+      <c r="E27" s="4"/>
     </row>
     <row r="28" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A28" s="18">
+      <c r="A28" s="16">
         <v>5</v>
       </c>
-      <c r="B28" s="19" t="s">
+      <c r="B28" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="C28" s="4"/>
-      <c r="D28" s="4"/>
-      <c r="E28" s="5"/>
+      <c r="C28" s="3"/>
+      <c r="D28" s="3"/>
+      <c r="E28" s="4"/>
     </row>
     <row r="29" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A29" s="18">
+      <c r="A29" s="16">
         <v>6</v>
       </c>
-      <c r="B29" s="19" t="s">
+      <c r="B29" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="C29" s="4"/>
-      <c r="D29" s="4"/>
-      <c r="E29" s="5"/>
+      <c r="C29" s="3"/>
+      <c r="D29" s="3"/>
+      <c r="E29" s="4"/>
     </row>
     <row r="30" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A30" s="18">
+      <c r="A30" s="16">
         <v>7</v>
       </c>
-      <c r="B30" s="19" t="s">
+      <c r="B30" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="C30" s="4"/>
-      <c r="D30" s="4"/>
-      <c r="E30" s="5"/>
+      <c r="C30" s="3"/>
+      <c r="D30" s="3"/>
+      <c r="E30" s="4"/>
     </row>
     <row r="31" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A31" s="20">
+      <c r="A31" s="18">
         <v>8</v>
       </c>
-      <c r="B31" s="21" t="s">
+      <c r="B31" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="C31" s="4"/>
-      <c r="D31" s="4"/>
-      <c r="E31" s="5"/>
+      <c r="C31" s="3"/>
+      <c r="D31" s="3"/>
+      <c r="E31" s="4"/>
     </row>
     <row r="32" spans="1:5" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="22"/>
-      <c r="B32" s="22"/>
-      <c r="C32" s="4"/>
-      <c r="D32" s="4"/>
-      <c r="E32" s="5"/>
+      <c r="A32" s="20"/>
+      <c r="B32" s="20"/>
+      <c r="C32" s="3"/>
+      <c r="D32" s="3"/>
+      <c r="E32" s="4"/>
     </row>
     <row r="33" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A33" s="17" t="s">
+      <c r="A33" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="B33" s="17"/>
-      <c r="C33" s="4"/>
-      <c r="D33" s="4"/>
-      <c r="E33" s="5"/>
+      <c r="B33" s="33"/>
+      <c r="C33" s="3"/>
+      <c r="D33" s="3"/>
+      <c r="E33" s="4"/>
     </row>
     <row r="34" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A34" s="18">
+      <c r="A34" s="16">
         <v>1</v>
       </c>
-      <c r="B34" s="19" t="s">
+      <c r="B34" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="C34" s="4"/>
-      <c r="D34" s="4"/>
-      <c r="E34" s="5"/>
+      <c r="C34" s="3"/>
+      <c r="D34" s="3"/>
+      <c r="E34" s="4"/>
     </row>
     <row r="35" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A35" s="18">
+      <c r="A35" s="16">
         <v>2</v>
       </c>
-      <c r="B35" s="23"/>
-      <c r="C35" s="4"/>
-      <c r="D35" s="4"/>
-      <c r="E35" s="5"/>
+      <c r="B35" s="21"/>
+      <c r="C35" s="3"/>
+      <c r="D35" s="3"/>
+      <c r="E35" s="4"/>
     </row>
     <row r="36" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A36" s="18">
+      <c r="A36" s="16">
         <v>3</v>
       </c>
-      <c r="B36" s="19" t="s">
+      <c r="B36" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="C36" s="4"/>
-      <c r="D36" s="4"/>
-      <c r="E36" s="5"/>
+      <c r="C36" s="3"/>
+      <c r="D36" s="3"/>
+      <c r="E36" s="4"/>
     </row>
     <row r="37" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A37" s="18">
+      <c r="A37" s="16">
         <v>4</v>
       </c>
-      <c r="B37" s="19" t="s">
+      <c r="B37" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="C37" s="4"/>
-      <c r="D37" s="4"/>
-      <c r="E37" s="5"/>
+      <c r="C37" s="3"/>
+      <c r="D37" s="3"/>
+      <c r="E37" s="4"/>
     </row>
     <row r="38" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A38" s="18">
+      <c r="A38" s="16">
         <v>5</v>
       </c>
-      <c r="B38" s="19" t="s">
+      <c r="B38" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="C38" s="4"/>
-      <c r="D38" s="4"/>
-      <c r="E38" s="5"/>
+      <c r="C38" s="3"/>
+      <c r="D38" s="3"/>
+      <c r="E38" s="4"/>
     </row>
     <row r="39" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A39" s="18">
+      <c r="A39" s="16">
         <v>6</v>
       </c>
-      <c r="B39" s="19" t="s">
+      <c r="B39" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="C39" s="4"/>
-      <c r="D39" s="4"/>
-      <c r="E39" s="5"/>
-    </row>
-    <row r="40" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A40" s="18">
+      <c r="C39" s="3"/>
+      <c r="D39" s="3"/>
+      <c r="E39" s="4"/>
+    </row>
+    <row r="40" spans="1:5" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A40" s="16">
         <v>7</v>
       </c>
-      <c r="B40" s="19" t="s">
+      <c r="B40" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="C40" s="4"/>
-      <c r="D40" s="4"/>
-      <c r="E40" s="5"/>
+      <c r="C40" s="3"/>
+      <c r="D40" s="3"/>
+      <c r="E40" s="4"/>
     </row>
     <row r="41" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A41" s="20">
+      <c r="A41" s="18">
         <v>8</v>
       </c>
-      <c r="B41" s="21" t="s">
+      <c r="B41" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="C41" s="4"/>
-      <c r="D41" s="4"/>
-      <c r="E41" s="5"/>
+      <c r="C41" s="3"/>
+      <c r="D41" s="3"/>
+      <c r="E41" s="4"/>
     </row>
     <row r="42" spans="1:5" ht="93.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="22"/>
-      <c r="B42" s="22"/>
-      <c r="C42" s="4"/>
-      <c r="D42" s="4"/>
-      <c r="E42" s="5"/>
+      <c r="A42" s="20"/>
+      <c r="B42" s="20"/>
+      <c r="C42" s="3"/>
+      <c r="D42" s="3"/>
+      <c r="E42" s="4"/>
     </row>
     <row r="43" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A43" s="17" t="s">
+      <c r="A43" s="33" t="s">
         <v>40</v>
       </c>
-      <c r="B43" s="17"/>
-      <c r="C43" s="4"/>
-      <c r="D43" s="4"/>
-      <c r="E43" s="5"/>
+      <c r="B43" s="33"/>
+      <c r="C43" s="3"/>
+      <c r="D43" s="3"/>
+      <c r="E43" s="4"/>
     </row>
     <row r="44" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A44" s="18">
+      <c r="A44" s="16">
         <v>1</v>
       </c>
-      <c r="B44" s="19" t="s">
+      <c r="B44" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="C44" s="4"/>
-      <c r="D44" s="4"/>
-      <c r="E44" s="5"/>
+      <c r="C44" s="3"/>
+      <c r="D44" s="3"/>
+      <c r="E44" s="4"/>
     </row>
     <row r="45" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A45" s="18">
+      <c r="A45" s="16">
         <v>2</v>
       </c>
-      <c r="B45" s="19" t="s">
+      <c r="B45" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="C45" s="4"/>
-      <c r="D45" s="4"/>
-      <c r="E45" s="5"/>
+      <c r="C45" s="3"/>
+      <c r="D45" s="3"/>
+      <c r="E45" s="4"/>
     </row>
     <row r="46" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A46" s="18">
+      <c r="A46" s="16">
         <v>3</v>
       </c>
-      <c r="B46" s="23"/>
-      <c r="C46" s="4"/>
-      <c r="D46" s="4"/>
-      <c r="E46" s="5"/>
+      <c r="B46" s="21"/>
+      <c r="C46" s="3"/>
+      <c r="D46" s="3"/>
+      <c r="E46" s="4"/>
     </row>
     <row r="47" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A47" s="18">
+      <c r="A47" s="16">
         <v>4</v>
       </c>
-      <c r="B47" s="19" t="s">
+      <c r="B47" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="C47" s="4"/>
-      <c r="D47" s="4"/>
-      <c r="E47" s="5"/>
+      <c r="C47" s="3"/>
+      <c r="D47" s="3"/>
+      <c r="E47" s="4"/>
     </row>
     <row r="48" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A48" s="18">
+      <c r="A48" s="16">
         <v>5</v>
       </c>
-      <c r="B48" s="19" t="s">
+      <c r="B48" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="C48" s="4"/>
-      <c r="D48" s="4"/>
-      <c r="E48" s="5"/>
+      <c r="C48" s="3"/>
+      <c r="D48" s="3"/>
+      <c r="E48" s="4"/>
     </row>
     <row r="49" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A49" s="18">
+      <c r="A49" s="16">
         <v>6</v>
       </c>
-      <c r="B49" s="19" t="s">
+      <c r="B49" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="C49" s="4"/>
-      <c r="D49" s="4"/>
-      <c r="E49" s="5"/>
+      <c r="C49" s="3"/>
+      <c r="D49" s="3"/>
+      <c r="E49" s="4"/>
     </row>
     <row r="50" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A50" s="18">
+      <c r="A50" s="16">
         <v>7</v>
       </c>
-      <c r="B50" s="19" t="s">
+      <c r="B50" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="C50" s="4"/>
-      <c r="D50" s="4"/>
-      <c r="E50" s="5"/>
+      <c r="C50" s="3"/>
+      <c r="D50" s="3"/>
+      <c r="E50" s="4"/>
     </row>
     <row r="51" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A51" s="20">
+      <c r="A51" s="18">
         <v>8</v>
       </c>
-      <c r="B51" s="21" t="s">
+      <c r="B51" s="19" t="s">
         <v>47</v>
       </c>
-      <c r="C51" s="4"/>
-      <c r="D51" s="4"/>
-      <c r="E51" s="5"/>
+      <c r="C51" s="3"/>
+      <c r="D51" s="3"/>
+      <c r="E51" s="4"/>
     </row>
     <row r="52" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A52" s="22"/>
-      <c r="B52" s="22"/>
-      <c r="C52" s="4"/>
-      <c r="D52" s="4"/>
-      <c r="E52" s="5"/>
+      <c r="A52" s="20"/>
+      <c r="B52" s="20"/>
+      <c r="C52" s="3"/>
+      <c r="D52" s="3"/>
+      <c r="E52" s="4"/>
     </row>
     <row r="53" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A53" s="22"/>
-      <c r="B53" s="22"/>
-      <c r="C53" s="4"/>
-      <c r="D53" s="4"/>
-      <c r="E53" s="5"/>
+      <c r="A53" s="20"/>
+      <c r="B53" s="20"/>
+      <c r="C53" s="3"/>
+      <c r="D53" s="3"/>
+      <c r="E53" s="4"/>
     </row>
     <row r="54" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="17" t="s">
+      <c r="A54" s="33" t="s">
         <v>48</v>
       </c>
-      <c r="B54" s="17"/>
-      <c r="C54" s="4"/>
-      <c r="D54" s="4"/>
-      <c r="E54" s="5"/>
+      <c r="B54" s="33"/>
+      <c r="C54" s="3"/>
+      <c r="D54" s="3"/>
+      <c r="E54" s="4"/>
     </row>
     <row r="55" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="18">
+      <c r="A55" s="16">
         <v>1</v>
       </c>
-      <c r="B55" s="19" t="s">
+      <c r="B55" s="17" t="s">
         <v>49</v>
       </c>
-      <c r="C55" s="4"/>
-      <c r="D55" s="4"/>
-      <c r="E55" s="5"/>
+      <c r="C55" s="3"/>
+      <c r="D55" s="3"/>
+      <c r="E55" s="4"/>
     </row>
     <row r="56" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A56" s="18">
+      <c r="A56" s="16">
         <v>2</v>
       </c>
-      <c r="B56" s="19" t="s">
+      <c r="B56" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="C56" s="4"/>
-      <c r="D56" s="4"/>
-      <c r="E56" s="5"/>
+      <c r="C56" s="3"/>
+      <c r="D56" s="3"/>
+      <c r="E56" s="4"/>
     </row>
     <row r="57" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A57" s="18">
+      <c r="A57" s="16">
         <v>3</v>
       </c>
-      <c r="B57" s="19" t="s">
+      <c r="B57" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="C57" s="4"/>
-      <c r="D57" s="4"/>
-      <c r="E57" s="5"/>
+      <c r="C57" s="3"/>
+      <c r="D57" s="3"/>
+      <c r="E57" s="4"/>
     </row>
     <row r="58" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A58" s="18">
+      <c r="A58" s="16">
         <v>4</v>
       </c>
-      <c r="B58" s="19" t="s">
+      <c r="B58" s="17" t="s">
         <v>52</v>
       </c>
-      <c r="C58" s="4"/>
-      <c r="D58" s="4"/>
-      <c r="E58" s="5"/>
+      <c r="C58" s="3"/>
+      <c r="D58" s="3"/>
+      <c r="E58" s="4"/>
     </row>
     <row r="59" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A59" s="18">
+      <c r="A59" s="16">
         <v>5</v>
       </c>
-      <c r="B59" s="19" t="s">
+      <c r="B59" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="C59" s="4"/>
-      <c r="D59" s="4"/>
-      <c r="E59" s="5"/>
+      <c r="C59" s="3"/>
+      <c r="D59" s="3"/>
+      <c r="E59" s="4"/>
     </row>
     <row r="60" spans="1:5" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="A60" s="18">
+      <c r="A60" s="16">
         <v>6</v>
       </c>
-      <c r="B60" s="19" t="s">
+      <c r="B60" s="17" t="s">
         <v>54</v>
       </c>
-      <c r="C60" s="4"/>
-      <c r="E60" s="5"/>
+      <c r="C60" s="3"/>
+      <c r="E60" s="4"/>
     </row>
     <row r="61" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A61" s="18">
+      <c r="A61" s="16">
         <v>7</v>
       </c>
-      <c r="B61" s="19" t="s">
+      <c r="B61" s="17" t="s">
         <v>55</v>
       </c>
-      <c r="C61" s="4"/>
-      <c r="D61" s="4"/>
-      <c r="E61" s="5"/>
+      <c r="C61" s="3"/>
+      <c r="D61" s="3"/>
+      <c r="E61" s="4"/>
     </row>
     <row r="62" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A62" s="20">
+      <c r="A62" s="18">
         <v>8</v>
       </c>
-      <c r="B62" s="21" t="s">
+      <c r="B62" s="19" t="s">
         <v>56</v>
       </c>
-      <c r="C62" s="4"/>
-      <c r="D62" s="4"/>
-      <c r="E62" s="5"/>
+      <c r="C62" s="3"/>
+      <c r="D62" s="3"/>
+      <c r="E62" s="4"/>
     </row>
     <row r="63" spans="1:5" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="22"/>
-      <c r="B63" s="22"/>
-      <c r="C63" s="4"/>
-      <c r="D63" s="4"/>
-      <c r="E63" s="5"/>
+      <c r="A63" s="20"/>
+      <c r="B63" s="20"/>
+      <c r="C63" s="3"/>
+      <c r="D63" s="3"/>
+      <c r="E63" s="4"/>
     </row>
     <row r="64" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A64" s="17" t="s">
+      <c r="A64" s="33" t="s">
         <v>57</v>
       </c>
-      <c r="B64" s="17"/>
-      <c r="C64" s="4"/>
-      <c r="D64" s="4"/>
-      <c r="E64" s="5"/>
+      <c r="B64" s="33"/>
+      <c r="C64" s="3"/>
+      <c r="D64" s="3"/>
+      <c r="E64" s="4"/>
     </row>
     <row r="65" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A65" s="18">
+      <c r="A65" s="16">
         <v>1</v>
       </c>
-      <c r="B65" s="23"/>
-      <c r="C65" s="4"/>
-      <c r="D65" s="4"/>
-      <c r="E65" s="5"/>
+      <c r="B65" s="35" t="s">
+        <v>154</v>
+      </c>
+      <c r="C65" s="3"/>
+      <c r="D65" s="3"/>
+      <c r="E65" s="4"/>
     </row>
     <row r="66" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A66" s="18">
+      <c r="A66" s="16">
         <v>2</v>
       </c>
-      <c r="B66" s="19" t="s">
+      <c r="B66" s="17" t="s">
         <v>58</v>
       </c>
-      <c r="C66" s="4"/>
-      <c r="D66" s="4"/>
-      <c r="E66" s="5"/>
+      <c r="C66" s="3"/>
+      <c r="D66" s="3"/>
+      <c r="E66" s="4"/>
     </row>
     <row r="67" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A67" s="18">
+      <c r="A67" s="16">
         <v>3</v>
       </c>
-      <c r="B67" s="19" t="s">
+      <c r="B67" s="17" t="s">
         <v>59</v>
       </c>
-      <c r="C67" s="4"/>
-      <c r="D67" s="34" t="s">
+      <c r="C67" s="3"/>
+      <c r="D67" s="30" t="s">
         <v>60</v>
       </c>
-      <c r="E67" s="5"/>
+      <c r="E67" s="4"/>
     </row>
     <row r="68" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A68" s="18">
+      <c r="A68" s="16">
         <v>4</v>
       </c>
-      <c r="B68" s="19" t="s">
+      <c r="B68" s="17" t="s">
         <v>61</v>
       </c>
-      <c r="C68" s="4"/>
-      <c r="D68" s="6" t="s">
+      <c r="C68" s="3"/>
+      <c r="D68" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="E68" s="5"/>
+      <c r="E68" s="4"/>
     </row>
     <row r="69" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A69" s="18">
+      <c r="A69" s="16">
         <v>5</v>
       </c>
-      <c r="B69" s="19" t="s">
+      <c r="B69" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="C69" s="4"/>
-      <c r="D69" s="6" t="s">
+      <c r="C69" s="3"/>
+      <c r="D69" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="E69" s="5"/>
+      <c r="E69" s="4"/>
     </row>
     <row r="70" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A70" s="18">
+      <c r="A70" s="16">
         <v>6</v>
       </c>
-      <c r="B70" s="24" t="s">
+      <c r="B70" s="22" t="s">
         <v>65</v>
       </c>
-      <c r="C70" s="4"/>
-      <c r="D70" s="4"/>
-      <c r="E70" s="5"/>
+      <c r="C70" s="3"/>
+      <c r="D70" s="3"/>
+      <c r="E70" s="4"/>
     </row>
     <row r="71" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A71" s="18">
+      <c r="A71" s="16">
         <v>7</v>
       </c>
-      <c r="B71" s="19" t="s">
+      <c r="B71" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="C71" s="4"/>
-      <c r="D71" s="4"/>
-      <c r="E71" s="5"/>
+      <c r="C71" s="3"/>
+      <c r="D71" s="3"/>
+      <c r="E71" s="4"/>
     </row>
     <row r="72" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A72" s="20">
+      <c r="A72" s="18">
         <v>8</v>
       </c>
-      <c r="B72" s="25" t="s">
+      <c r="B72" s="23" t="s">
         <v>67</v>
       </c>
-      <c r="C72" s="4"/>
-      <c r="D72" s="4"/>
-      <c r="E72" s="5"/>
+      <c r="C72" s="3"/>
+      <c r="D72" s="3"/>
+      <c r="E72" s="4"/>
     </row>
     <row r="73" spans="1:5" ht="9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A73" s="22"/>
-      <c r="B73" s="22"/>
-      <c r="C73" s="4"/>
-      <c r="D73" s="4"/>
-      <c r="E73" s="5"/>
+      <c r="A73" s="20"/>
+      <c r="B73" s="20"/>
+      <c r="C73" s="3"/>
+      <c r="D73" s="3"/>
+      <c r="E73" s="4"/>
     </row>
     <row r="74" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A74" s="17" t="s">
+      <c r="A74" s="33" t="s">
         <v>68</v>
       </c>
-      <c r="B74" s="17"/>
-      <c r="C74" s="4"/>
-      <c r="D74" s="4"/>
-      <c r="E74" s="5"/>
+      <c r="B74" s="33"/>
+      <c r="C74" s="3"/>
+      <c r="D74" s="3"/>
+      <c r="E74" s="4"/>
     </row>
     <row r="75" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A75" s="18">
+      <c r="A75" s="16">
         <v>1</v>
       </c>
-      <c r="B75" s="19" t="s">
+      <c r="B75" s="17" t="s">
         <v>69</v>
       </c>
-      <c r="C75" s="4"/>
-      <c r="D75" s="4"/>
-      <c r="E75" s="5"/>
+      <c r="C75" s="3"/>
+      <c r="D75" s="3"/>
+      <c r="E75" s="4"/>
     </row>
     <row r="76" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A76" s="18">
+      <c r="A76" s="16">
         <v>2</v>
       </c>
-      <c r="B76" s="19" t="s">
+      <c r="B76" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="C76" s="4"/>
-      <c r="D76" s="4"/>
-      <c r="E76" s="5"/>
+      <c r="C76" s="3"/>
+      <c r="D76" s="3"/>
+      <c r="E76" s="4"/>
     </row>
     <row r="77" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A77" s="18">
+      <c r="A77" s="16">
         <v>3</v>
       </c>
-      <c r="B77" s="19" t="s">
+      <c r="B77" s="17" t="s">
         <v>71</v>
       </c>
-      <c r="C77" s="4"/>
-      <c r="D77" s="4"/>
-      <c r="E77" s="5"/>
+      <c r="C77" s="3"/>
+      <c r="D77" s="3"/>
+      <c r="E77" s="4"/>
     </row>
     <row r="78" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A78" s="18">
+      <c r="A78" s="16">
         <v>4</v>
       </c>
-      <c r="B78" s="19" t="s">
+      <c r="B78" s="17" t="s">
         <v>72</v>
       </c>
-      <c r="C78" s="4"/>
-      <c r="D78" s="4"/>
-      <c r="E78" s="5"/>
+      <c r="C78" s="3"/>
+      <c r="D78" s="3"/>
+      <c r="E78" s="4"/>
     </row>
     <row r="79" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A79" s="18">
+      <c r="A79" s="16">
         <v>5</v>
       </c>
-      <c r="B79" s="19" t="s">
+      <c r="B79" s="17" t="s">
         <v>73</v>
       </c>
-      <c r="C79" s="4"/>
-      <c r="D79" s="4"/>
-      <c r="E79" s="5"/>
+      <c r="C79" s="3"/>
+      <c r="D79" s="3"/>
+      <c r="E79" s="4"/>
     </row>
     <row r="80" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A80" s="18">
+      <c r="A80" s="16">
         <v>6</v>
       </c>
-      <c r="B80" s="23"/>
-      <c r="C80" s="4"/>
-      <c r="D80" s="4"/>
-      <c r="E80" s="5"/>
+      <c r="B80" s="21"/>
+      <c r="C80" s="3"/>
+      <c r="D80" s="3"/>
+      <c r="E80" s="4"/>
     </row>
     <row r="81" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A81" s="18">
+      <c r="A81" s="16">
         <v>7</v>
       </c>
-      <c r="B81" s="23"/>
-      <c r="C81" s="4"/>
-      <c r="D81" s="4"/>
-      <c r="E81" s="5"/>
+      <c r="B81" s="21"/>
+      <c r="C81" s="3"/>
+      <c r="D81" s="3"/>
+      <c r="E81" s="4"/>
     </row>
     <row r="82" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A82" s="20">
+      <c r="A82" s="18">
         <v>8</v>
       </c>
-      <c r="B82" s="26"/>
-      <c r="C82" s="4"/>
-      <c r="D82" s="4"/>
-      <c r="E82" s="5"/>
+      <c r="B82" s="24"/>
+      <c r="C82" s="3"/>
+      <c r="D82" s="3"/>
+      <c r="E82" s="4"/>
     </row>
     <row r="83" spans="1:5" ht="4.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A83" s="22"/>
-      <c r="B83" s="22"/>
-      <c r="C83" s="4"/>
-      <c r="D83" s="4"/>
-      <c r="E83" s="5"/>
+      <c r="A83" s="20"/>
+      <c r="B83" s="20"/>
+      <c r="C83" s="3"/>
+      <c r="D83" s="3"/>
+      <c r="E83" s="4"/>
     </row>
     <row r="84" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A84" s="27" t="s">
+      <c r="A84" s="31" t="s">
         <v>74</v>
       </c>
-      <c r="B84" s="27"/>
-      <c r="C84" s="4"/>
-      <c r="D84" s="4"/>
-      <c r="E84" s="5"/>
+      <c r="B84" s="31"/>
+      <c r="C84" s="3"/>
+      <c r="D84" s="3"/>
+      <c r="E84" s="4"/>
     </row>
     <row r="85" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A85" s="18">
+      <c r="A85" s="16">
         <v>1</v>
       </c>
-      <c r="B85" s="19" t="s">
+      <c r="B85" s="17" t="s">
         <v>75</v>
       </c>
-      <c r="C85" s="4"/>
-      <c r="D85" s="4"/>
-      <c r="E85" s="5"/>
+      <c r="C85" s="3"/>
+      <c r="D85" s="3"/>
+      <c r="E85" s="4"/>
     </row>
     <row r="86" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A86" s="18">
+      <c r="A86" s="16">
         <v>2</v>
       </c>
-      <c r="B86" s="19" t="s">
+      <c r="B86" s="17" t="s">
         <v>76</v>
       </c>
-      <c r="C86" s="4"/>
-      <c r="D86" s="4"/>
-      <c r="E86" s="5"/>
+      <c r="C86" s="3"/>
+      <c r="D86" s="3"/>
+      <c r="E86" s="4"/>
     </row>
     <row r="87" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A87" s="18">
+      <c r="A87" s="16">
         <v>3</v>
       </c>
-      <c r="B87" s="19" t="s">
+      <c r="B87" s="17" t="s">
         <v>77</v>
       </c>
-      <c r="C87" s="4"/>
-      <c r="D87" s="4"/>
-      <c r="E87" s="5"/>
+      <c r="C87" s="3"/>
+      <c r="D87" s="3"/>
+      <c r="E87" s="4"/>
     </row>
     <row r="88" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A88" s="18">
+      <c r="A88" s="16">
         <v>4</v>
       </c>
-      <c r="B88" s="19" t="s">
+      <c r="B88" s="17" t="s">
         <v>78</v>
       </c>
-      <c r="C88" s="4"/>
-      <c r="D88" s="4"/>
-      <c r="E88" s="5"/>
+      <c r="C88" s="3"/>
+      <c r="D88" s="3"/>
+      <c r="E88" s="4"/>
     </row>
     <row r="89" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A89" s="18">
+      <c r="A89" s="16">
         <v>5</v>
       </c>
-      <c r="B89" s="19" t="s">
+      <c r="B89" s="17" t="s">
         <v>79</v>
       </c>
-      <c r="C89" s="4"/>
-      <c r="D89" s="4"/>
-      <c r="E89" s="5"/>
-    </row>
-    <row r="90" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A90" s="18">
+      <c r="C89" s="3"/>
+      <c r="D89" s="3"/>
+      <c r="E89" s="4"/>
+    </row>
+    <row r="90" spans="1:5" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A90" s="16">
         <v>6</v>
       </c>
-      <c r="B90" s="19" t="s">
+      <c r="B90" s="17" t="s">
         <v>80</v>
       </c>
-      <c r="C90" s="4"/>
-      <c r="D90" s="4"/>
-      <c r="E90" s="5"/>
+      <c r="C90" s="3"/>
+      <c r="D90" s="3"/>
+      <c r="E90" s="4"/>
     </row>
     <row r="91" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A91" s="18">
+      <c r="A91" s="16">
         <v>7</v>
       </c>
-      <c r="B91" s="19" t="s">
+      <c r="B91" s="17" t="s">
         <v>81</v>
       </c>
-      <c r="C91" s="4"/>
-      <c r="D91" s="4"/>
-      <c r="E91" s="5"/>
+      <c r="C91" s="3"/>
+      <c r="D91" s="3"/>
+      <c r="E91" s="4"/>
     </row>
     <row r="92" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A92" s="20">
+      <c r="A92" s="18">
         <v>8</v>
       </c>
-      <c r="B92" s="21" t="s">
+      <c r="B92" s="19" t="s">
         <v>82</v>
       </c>
-      <c r="C92" s="4"/>
-      <c r="D92" s="4"/>
-      <c r="E92" s="5"/>
+      <c r="C92" s="3"/>
+      <c r="D92" s="3"/>
+      <c r="E92" s="4"/>
     </row>
     <row r="93" spans="1:5" ht="6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A93" s="22"/>
-      <c r="B93" s="22"/>
-      <c r="C93" s="4"/>
-      <c r="D93" s="4"/>
-      <c r="E93" s="5"/>
+      <c r="A93" s="20"/>
+      <c r="B93" s="20"/>
+      <c r="C93" s="3"/>
+      <c r="D93" s="3"/>
+      <c r="E93" s="4"/>
     </row>
     <row r="94" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A94" s="27" t="s">
+      <c r="A94" s="31" t="s">
         <v>83</v>
       </c>
-      <c r="B94" s="27"/>
-      <c r="C94" s="4"/>
-      <c r="D94" s="4"/>
-      <c r="E94" s="5"/>
+      <c r="B94" s="31"/>
+      <c r="C94" s="3"/>
+      <c r="D94" s="3"/>
+      <c r="E94" s="4"/>
     </row>
     <row r="95" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A95" s="18">
+      <c r="A95" s="16">
         <v>1</v>
       </c>
-      <c r="B95" s="19" t="s">
+      <c r="B95" s="17" t="s">
         <v>84</v>
       </c>
-      <c r="C95" s="4"/>
-      <c r="D95" s="4"/>
-      <c r="E95" s="5"/>
+      <c r="C95" s="3"/>
+      <c r="D95" s="3"/>
+      <c r="E95" s="4"/>
     </row>
     <row r="96" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A96" s="18">
+      <c r="A96" s="16">
         <v>2</v>
       </c>
-      <c r="B96" s="19" t="s">
+      <c r="B96" s="17" t="s">
         <v>85</v>
       </c>
-      <c r="C96" s="4"/>
-      <c r="D96" s="4"/>
-      <c r="E96" s="5"/>
+      <c r="C96" s="3"/>
+      <c r="D96" s="3"/>
+      <c r="E96" s="4"/>
     </row>
     <row r="97" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A97" s="18">
+      <c r="A97" s="16">
         <v>3</v>
       </c>
-      <c r="B97" s="19" t="s">
+      <c r="B97" s="17" t="s">
         <v>86</v>
       </c>
-      <c r="C97" s="4"/>
-      <c r="D97" s="4"/>
-      <c r="E97" s="5"/>
+      <c r="C97" s="3"/>
+      <c r="D97" s="3"/>
+      <c r="E97" s="4"/>
     </row>
     <row r="98" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A98" s="18">
+      <c r="A98" s="16">
         <v>4</v>
       </c>
-      <c r="B98" s="19" t="s">
+      <c r="B98" s="17" t="s">
         <v>87</v>
       </c>
-      <c r="C98" s="4"/>
-      <c r="D98" s="4"/>
-      <c r="E98" s="5"/>
+      <c r="C98" s="3"/>
+      <c r="D98" s="3"/>
+      <c r="E98" s="4"/>
     </row>
     <row r="99" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A99" s="18">
+      <c r="A99" s="16">
         <v>5</v>
       </c>
-      <c r="B99" s="19" t="s">
+      <c r="B99" s="17" t="s">
         <v>88</v>
       </c>
-      <c r="C99" s="4"/>
-      <c r="D99" s="4"/>
-      <c r="E99" s="5"/>
+      <c r="C99" s="3"/>
+      <c r="D99" s="3"/>
+      <c r="E99" s="4"/>
     </row>
     <row r="100" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A100" s="18">
+      <c r="A100" s="16">
         <v>6</v>
       </c>
-      <c r="B100" s="19" t="s">
+      <c r="B100" s="17" t="s">
         <v>89</v>
       </c>
-      <c r="C100" s="4"/>
-      <c r="D100" s="4"/>
-      <c r="E100" s="5"/>
+      <c r="C100" s="3"/>
+      <c r="D100" s="3"/>
+      <c r="E100" s="4"/>
     </row>
     <row r="101" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A101" s="18">
+      <c r="A101" s="16">
         <v>7</v>
       </c>
-      <c r="B101" s="19" t="s">
+      <c r="B101" s="17" t="s">
         <v>90</v>
       </c>
-      <c r="C101" s="4"/>
-      <c r="D101" s="4"/>
-      <c r="E101" s="5"/>
+      <c r="C101" s="3"/>
+      <c r="D101" s="3"/>
+      <c r="E101" s="4"/>
     </row>
     <row r="102" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A102" s="20">
+      <c r="A102" s="18">
         <v>8</v>
       </c>
-      <c r="B102" s="21" t="s">
+      <c r="B102" s="19" t="s">
         <v>91</v>
       </c>
-      <c r="C102" s="4"/>
-      <c r="D102" s="4"/>
-      <c r="E102" s="5"/>
+      <c r="C102" s="3"/>
+      <c r="D102" s="3"/>
+      <c r="E102" s="4"/>
     </row>
     <row r="103" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A103" s="22"/>
-      <c r="B103" s="22"/>
-      <c r="C103" s="4"/>
-      <c r="D103" s="4"/>
-      <c r="E103" s="5"/>
+      <c r="A103" s="20"/>
+      <c r="B103" s="20"/>
+      <c r="C103" s="3"/>
+      <c r="D103" s="3"/>
+      <c r="E103" s="4"/>
     </row>
     <row r="104" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A104" s="28" t="s">
+      <c r="A104" s="32" t="s">
         <v>92</v>
       </c>
-      <c r="B104" s="28"/>
-      <c r="C104" s="4"/>
-      <c r="D104" s="4"/>
-      <c r="E104" s="5"/>
+      <c r="B104" s="32"/>
+      <c r="C104" s="3"/>
+      <c r="D104" s="3"/>
+      <c r="E104" s="4"/>
     </row>
     <row r="105" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A105" s="29">
+      <c r="A105" s="25">
         <v>1</v>
       </c>
-      <c r="B105" s="30" t="s">
+      <c r="B105" s="26" t="s">
         <v>93</v>
       </c>
-      <c r="C105" s="4"/>
-      <c r="D105" s="4"/>
-      <c r="E105" s="5"/>
+      <c r="C105" s="3"/>
+      <c r="D105" s="3"/>
+      <c r="E105" s="4"/>
     </row>
     <row r="106" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A106" s="29">
+      <c r="A106" s="25">
         <v>2</v>
       </c>
-      <c r="B106" s="30" t="s">
+      <c r="B106" s="26" t="s">
         <v>94</v>
       </c>
-      <c r="C106" s="4"/>
-      <c r="D106" s="4"/>
-      <c r="E106" s="5"/>
+      <c r="C106" s="3"/>
+      <c r="D106" s="3"/>
+      <c r="E106" s="4"/>
     </row>
     <row r="107" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A107" s="29">
+      <c r="A107" s="25">
         <v>3</v>
       </c>
-      <c r="B107" s="30" t="s">
+      <c r="B107" s="26" t="s">
         <v>95</v>
       </c>
-      <c r="C107" s="4"/>
-      <c r="D107" s="4"/>
-      <c r="E107" s="5"/>
+      <c r="C107" s="3"/>
+      <c r="D107" s="3"/>
+      <c r="E107" s="4"/>
     </row>
     <row r="108" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A108" s="29">
+      <c r="A108" s="25">
         <v>4</v>
       </c>
-      <c r="B108" s="30" t="s">
+      <c r="B108" s="26" t="s">
         <v>96</v>
       </c>
-      <c r="C108" s="4"/>
-      <c r="D108" s="4"/>
-      <c r="E108" s="5"/>
+      <c r="C108" s="3"/>
+      <c r="D108" s="3"/>
+      <c r="E108" s="4"/>
     </row>
     <row r="109" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A109" s="29">
+      <c r="A109" s="25">
         <v>5</v>
       </c>
-      <c r="B109" s="30" t="s">
+      <c r="B109" s="26" t="s">
         <v>97</v>
       </c>
-      <c r="C109" s="4"/>
-      <c r="D109" s="4"/>
-      <c r="E109" s="5"/>
-    </row>
-    <row r="110" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A110" s="29">
+      <c r="C109" s="3"/>
+      <c r="D109" s="3"/>
+      <c r="E109" s="4"/>
+    </row>
+    <row r="110" spans="1:5" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A110" s="25">
         <v>6</v>
       </c>
-      <c r="B110" s="30" t="s">
+      <c r="B110" s="26" t="s">
         <v>98</v>
       </c>
-      <c r="C110" s="4"/>
-      <c r="D110" s="4"/>
-      <c r="E110" s="5"/>
+      <c r="C110" s="3"/>
+      <c r="D110" s="3"/>
+      <c r="E110" s="4"/>
     </row>
     <row r="111" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A111" s="31">
+      <c r="A111" s="27">
         <v>7</v>
       </c>
-      <c r="B111" s="32" t="s">
+      <c r="B111" s="28" t="s">
         <v>99</v>
       </c>
-      <c r="C111" s="4"/>
-      <c r="D111" s="4"/>
-      <c r="E111" s="5"/>
+      <c r="C111" s="3"/>
+      <c r="D111" s="3"/>
+      <c r="E111" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="A33:B33"/>
     <mergeCell ref="A94:B94"/>
     <mergeCell ref="A104:B104"/>
     <mergeCell ref="A43:B43"/>
@@ -2221,11 +2240,6 @@
     <mergeCell ref="A64:B64"/>
     <mergeCell ref="A74:B74"/>
     <mergeCell ref="A84:B84"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="A33:B33"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -2240,495 +2254,495 @@
   <dimension ref="A1:C54"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="18" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="5.88671875" style="8" customWidth="1"/>
-    <col min="2" max="2" width="36.77734375" style="13" customWidth="1"/>
-    <col min="3" max="3" width="36.33203125" style="9" customWidth="1"/>
-    <col min="4" max="16384" width="8.6640625" style="9"/>
+    <col min="1" max="1" width="5.88671875" style="7" customWidth="1"/>
+    <col min="2" max="2" width="36.77734375" style="12" customWidth="1"/>
+    <col min="3" max="3" width="36.33203125" style="8" customWidth="1"/>
+    <col min="4" max="16384" width="8.6640625" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="15" t="s">
+    <row r="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="14" t="s">
         <v>153</v>
       </c>
-      <c r="B1" s="16" t="s">
+      <c r="B1" s="15" t="s">
         <v>152</v>
       </c>
-      <c r="C1" s="15"/>
+      <c r="C1" s="14"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A2" s="10">
+      <c r="A2" s="9">
         <v>1</v>
       </c>
-      <c r="B2" s="14" t="s">
+      <c r="B2" s="13" t="s">
         <v>100</v>
       </c>
-      <c r="C2" s="11"/>
+      <c r="C2" s="10"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A3" s="10">
+      <c r="A3" s="9">
         <v>2</v>
       </c>
-      <c r="B3" s="14" t="s">
+      <c r="B3" s="13" t="s">
         <v>101</v>
       </c>
-      <c r="C3" s="11"/>
+      <c r="C3" s="10"/>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A4" s="10">
+      <c r="A4" s="9">
         <v>3</v>
       </c>
-      <c r="B4" s="14" t="s">
+      <c r="B4" s="13" t="s">
         <v>102</v>
       </c>
-      <c r="C4" s="11"/>
+      <c r="C4" s="10"/>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A5" s="10">
+      <c r="A5" s="9">
         <v>4</v>
       </c>
-      <c r="B5" s="14" t="s">
+      <c r="B5" s="13" t="s">
         <v>103</v>
       </c>
-      <c r="C5" s="11"/>
+      <c r="C5" s="10"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A6" s="10">
+      <c r="A6" s="9">
         <v>5</v>
       </c>
-      <c r="B6" s="14" t="s">
+      <c r="B6" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="C6" s="11"/>
+      <c r="C6" s="10"/>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A7" s="10">
+      <c r="A7" s="9">
         <v>6</v>
       </c>
-      <c r="B7" s="14" t="s">
+      <c r="B7" s="13" t="s">
         <v>105</v>
       </c>
-      <c r="C7" s="11"/>
+      <c r="C7" s="10"/>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A8" s="10">
+      <c r="A8" s="9">
         <v>7</v>
       </c>
-      <c r="B8" s="14" t="s">
+      <c r="B8" s="13" t="s">
         <v>106</v>
       </c>
-      <c r="C8" s="11"/>
+      <c r="C8" s="10"/>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A9" s="10">
+      <c r="A9" s="9">
         <v>8</v>
       </c>
-      <c r="B9" s="14" t="s">
+      <c r="B9" s="13" t="s">
         <v>107</v>
       </c>
-      <c r="C9" s="11"/>
+      <c r="C9" s="10"/>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A10" s="10">
+      <c r="A10" s="9">
         <v>9</v>
       </c>
-      <c r="B10" s="14" t="s">
+      <c r="B10" s="13" t="s">
         <v>108</v>
       </c>
-      <c r="C10" s="11"/>
+      <c r="C10" s="10"/>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A11" s="10">
+      <c r="A11" s="9">
         <v>10</v>
       </c>
-      <c r="B11" s="14" t="s">
+      <c r="B11" s="13" t="s">
         <v>109</v>
       </c>
-      <c r="C11" s="11"/>
+      <c r="C11" s="10"/>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A12" s="10">
+      <c r="A12" s="9">
         <v>11</v>
       </c>
-      <c r="B12" s="14" t="s">
+      <c r="B12" s="13" t="s">
         <v>110</v>
       </c>
-      <c r="C12" s="11"/>
+      <c r="C12" s="10"/>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A13" s="10">
+      <c r="A13" s="9">
         <v>12</v>
       </c>
-      <c r="B13" s="14" t="s">
+      <c r="B13" s="13" t="s">
         <v>111</v>
       </c>
-      <c r="C13" s="11"/>
+      <c r="C13" s="10"/>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A14" s="10">
+      <c r="A14" s="9">
         <v>13</v>
       </c>
-      <c r="B14" s="14" t="s">
+      <c r="B14" s="13" t="s">
         <v>112</v>
       </c>
-      <c r="C14" s="11"/>
+      <c r="C14" s="10"/>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A15" s="10">
+      <c r="A15" s="9">
         <v>14</v>
       </c>
-      <c r="B15" s="14" t="s">
+      <c r="B15" s="13" t="s">
         <v>113</v>
       </c>
-      <c r="C15" s="11"/>
+      <c r="C15" s="10"/>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A16" s="10">
+      <c r="A16" s="9">
         <v>15</v>
       </c>
-      <c r="B16" s="14" t="s">
+      <c r="B16" s="13" t="s">
         <v>114</v>
       </c>
-      <c r="C16" s="11"/>
+      <c r="C16" s="10"/>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A17" s="10">
+      <c r="A17" s="9">
         <v>16</v>
       </c>
-      <c r="B17" s="14" t="s">
+      <c r="B17" s="13" t="s">
         <v>115</v>
       </c>
-      <c r="C17" s="11"/>
+      <c r="C17" s="10"/>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A18" s="10">
+      <c r="A18" s="9">
         <v>17</v>
       </c>
-      <c r="B18" s="14" t="s">
+      <c r="B18" s="13" t="s">
         <v>116</v>
       </c>
-      <c r="C18" s="11"/>
+      <c r="C18" s="10"/>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A19" s="10">
+      <c r="A19" s="9">
         <v>18</v>
       </c>
-      <c r="B19" s="14" t="s">
+      <c r="B19" s="13" t="s">
         <v>117</v>
       </c>
-      <c r="C19" s="11"/>
+      <c r="C19" s="10"/>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A20" s="10">
+      <c r="A20" s="9">
         <v>19</v>
       </c>
-      <c r="B20" s="14" t="s">
+      <c r="B20" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="C20" s="11"/>
+      <c r="C20" s="10"/>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A21" s="10">
+      <c r="A21" s="9">
         <v>20</v>
       </c>
-      <c r="B21" s="14" t="s">
+      <c r="B21" s="13" t="s">
         <v>119</v>
       </c>
-      <c r="C21" s="11"/>
+      <c r="C21" s="10"/>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A22" s="10">
+      <c r="A22" s="9">
         <v>21</v>
       </c>
-      <c r="B22" s="14" t="s">
+      <c r="B22" s="13" t="s">
         <v>120</v>
       </c>
-      <c r="C22" s="11"/>
+      <c r="C22" s="10"/>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A23" s="10">
+      <c r="A23" s="9">
         <v>22</v>
       </c>
-      <c r="B23" s="14" t="s">
+      <c r="B23" s="13" t="s">
         <v>121</v>
       </c>
-      <c r="C23" s="11"/>
+      <c r="C23" s="10"/>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A24" s="10">
+      <c r="A24" s="9">
         <v>23</v>
       </c>
-      <c r="B24" s="14" t="s">
+      <c r="B24" s="13" t="s">
         <v>122</v>
       </c>
-      <c r="C24" s="11"/>
+      <c r="C24" s="10"/>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A25" s="10">
+      <c r="A25" s="9">
         <v>24</v>
       </c>
-      <c r="B25" s="14" t="s">
+      <c r="B25" s="13" t="s">
         <v>123</v>
       </c>
-      <c r="C25" s="11"/>
+      <c r="C25" s="10"/>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A26" s="10">
+      <c r="A26" s="9">
         <v>25</v>
       </c>
-      <c r="B26" s="14" t="s">
+      <c r="B26" s="13" t="s">
         <v>124</v>
       </c>
-      <c r="C26" s="11"/>
+      <c r="C26" s="10"/>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A27" s="10">
+      <c r="A27" s="9">
         <v>26</v>
       </c>
-      <c r="B27" s="14" t="s">
+      <c r="B27" s="13" t="s">
         <v>125</v>
       </c>
-      <c r="C27" s="11"/>
+      <c r="C27" s="10"/>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A28" s="10">
+      <c r="A28" s="9">
         <v>27</v>
       </c>
-      <c r="B28" s="14" t="s">
+      <c r="B28" s="13" t="s">
         <v>126</v>
       </c>
-      <c r="C28" s="11"/>
+      <c r="C28" s="10"/>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A29" s="10">
+      <c r="A29" s="9">
         <v>28</v>
       </c>
-      <c r="B29" s="14" t="s">
+      <c r="B29" s="13" t="s">
         <v>127</v>
       </c>
-      <c r="C29" s="11"/>
+      <c r="C29" s="10"/>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A30" s="10">
+      <c r="A30" s="9">
         <v>29</v>
       </c>
-      <c r="B30" s="14" t="s">
+      <c r="B30" s="13" t="s">
         <v>128</v>
       </c>
-      <c r="C30" s="11"/>
+      <c r="C30" s="10"/>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A31" s="10">
+      <c r="A31" s="9">
         <v>30</v>
       </c>
-      <c r="B31" s="14" t="s">
+      <c r="B31" s="13" t="s">
         <v>129</v>
       </c>
-      <c r="C31" s="11"/>
+      <c r="C31" s="10"/>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A32" s="10">
+      <c r="A32" s="9">
         <v>31</v>
       </c>
-      <c r="B32" s="14" t="s">
+      <c r="B32" s="13" t="s">
         <v>130</v>
       </c>
-      <c r="C32" s="11"/>
+      <c r="C32" s="10"/>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A33" s="10">
+      <c r="A33" s="9">
         <v>32</v>
       </c>
-      <c r="B33" s="14" t="s">
+      <c r="B33" s="13" t="s">
         <v>131</v>
       </c>
-      <c r="C33" s="11"/>
+      <c r="C33" s="10"/>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A34" s="10">
+      <c r="A34" s="9">
         <v>33</v>
       </c>
-      <c r="B34" s="14" t="s">
+      <c r="B34" s="13" t="s">
         <v>132</v>
       </c>
-      <c r="C34" s="11"/>
+      <c r="C34" s="10"/>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A35" s="10">
+      <c r="A35" s="9">
         <v>34</v>
       </c>
-      <c r="B35" s="14" t="s">
+      <c r="B35" s="13" t="s">
         <v>133</v>
       </c>
-      <c r="C35" s="11"/>
+      <c r="C35" s="10"/>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A36" s="10">
+      <c r="A36" s="9">
         <v>35</v>
       </c>
-      <c r="B36" s="14" t="s">
+      <c r="B36" s="13" t="s">
         <v>134</v>
       </c>
-      <c r="C36" s="11"/>
+      <c r="C36" s="10"/>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A37" s="10">
+      <c r="A37" s="9">
         <v>36</v>
       </c>
-      <c r="B37" s="14" t="s">
+      <c r="B37" s="13" t="s">
         <v>135</v>
       </c>
-      <c r="C37" s="11"/>
+      <c r="C37" s="10"/>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A38" s="10">
+      <c r="A38" s="9">
         <v>37</v>
       </c>
-      <c r="B38" s="14" t="s">
+      <c r="B38" s="13" t="s">
         <v>136</v>
       </c>
-      <c r="C38" s="11"/>
+      <c r="C38" s="10"/>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A39" s="10">
+      <c r="A39" s="9">
         <v>38</v>
       </c>
-      <c r="B39" s="14" t="s">
+      <c r="B39" s="13" t="s">
         <v>137</v>
       </c>
-      <c r="C39" s="11"/>
+      <c r="C39" s="10"/>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A40" s="10">
+      <c r="A40" s="9">
         <v>39</v>
       </c>
-      <c r="B40" s="14" t="s">
+      <c r="B40" s="13" t="s">
         <v>138</v>
       </c>
-      <c r="C40" s="11"/>
+      <c r="C40" s="10"/>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A41" s="10">
+      <c r="A41" s="9">
         <v>40</v>
       </c>
-      <c r="B41" s="14" t="s">
+      <c r="B41" s="13" t="s">
         <v>139</v>
       </c>
-      <c r="C41" s="11"/>
+      <c r="C41" s="10"/>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A42" s="10">
+      <c r="A42" s="9">
         <v>41</v>
       </c>
-      <c r="B42" s="14" t="s">
+      <c r="B42" s="13" t="s">
         <v>140</v>
       </c>
-      <c r="C42" s="11"/>
+      <c r="C42" s="10"/>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A43" s="10">
+      <c r="A43" s="9">
         <v>42</v>
       </c>
-      <c r="B43" s="14" t="s">
+      <c r="B43" s="13" t="s">
         <v>141</v>
       </c>
-      <c r="C43" s="11"/>
+      <c r="C43" s="10"/>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A44" s="10">
+      <c r="A44" s="9">
         <v>43</v>
       </c>
-      <c r="B44" s="14" t="s">
+      <c r="B44" s="13" t="s">
         <v>142</v>
       </c>
-      <c r="C44" s="11"/>
+      <c r="C44" s="10"/>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A45" s="10">
+      <c r="A45" s="9">
         <v>44</v>
       </c>
-      <c r="B45" s="12" t="s">
+      <c r="B45" s="11" t="s">
         <v>143</v>
       </c>
-      <c r="C45" s="11"/>
+      <c r="C45" s="10"/>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A46" s="10">
+      <c r="A46" s="9">
         <v>45</v>
       </c>
-      <c r="B46" s="12" t="s">
+      <c r="B46" s="11" t="s">
         <v>144</v>
       </c>
-      <c r="C46" s="11"/>
+      <c r="C46" s="10"/>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A47" s="10">
+      <c r="A47" s="9">
         <v>46</v>
       </c>
-      <c r="B47" s="12" t="s">
+      <c r="B47" s="11" t="s">
         <v>145</v>
       </c>
-      <c r="C47" s="11"/>
+      <c r="C47" s="10"/>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A48" s="10">
+      <c r="A48" s="9">
         <v>47</v>
       </c>
-      <c r="B48" s="12" t="s">
+      <c r="B48" s="11" t="s">
         <v>146</v>
       </c>
-      <c r="C48" s="11"/>
+      <c r="C48" s="10"/>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A49" s="10">
+      <c r="A49" s="9">
         <v>48</v>
       </c>
-      <c r="B49" s="12" t="s">
+      <c r="B49" s="11" t="s">
         <v>147</v>
       </c>
-      <c r="C49" s="11"/>
+      <c r="C49" s="10"/>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A50" s="10">
+      <c r="A50" s="9">
         <v>49</v>
       </c>
-      <c r="B50" s="12" t="s">
+      <c r="B50" s="11" t="s">
         <v>148</v>
       </c>
-      <c r="C50" s="11"/>
+      <c r="C50" s="10"/>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A51" s="10">
+      <c r="A51" s="9">
         <v>50</v>
       </c>
-      <c r="B51" s="12" t="s">
+      <c r="B51" s="11" t="s">
         <v>149</v>
       </c>
-      <c r="C51" s="11"/>
+      <c r="C51" s="10"/>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A52" s="10">
+      <c r="A52" s="9">
         <v>51</v>
       </c>
-      <c r="B52" s="12" t="s">
+      <c r="B52" s="11" t="s">
         <v>150</v>
       </c>
-      <c r="C52" s="11"/>
+      <c r="C52" s="10"/>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A53" s="10">
+      <c r="A53" s="9">
         <v>52</v>
       </c>
-      <c r="B53" s="12" t="s">
+      <c r="B53" s="11" t="s">
         <v>151</v>
       </c>
-      <c r="C53" s="11"/>
+      <c r="C53" s="10"/>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A54" s="10">
+      <c r="A54" s="9">
         <v>53</v>
       </c>
-      <c r="B54" s="12"/>
-      <c r="C54" s="11"/>
+      <c r="B54" s="11"/>
+      <c r="C54" s="10"/>
     </row>
   </sheetData>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/HA/home/таблица.xlsx
+++ b/HA/home/таблица.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\_GitHub\python_prj\HA\home\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65D53054-29CB-4686-8896-B92BFA1B18DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19CFCBA1-1E7B-44AE-B3F8-2570CDC5979A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -790,20 +790,20 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -888,6 +888,61 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>137160</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>182880</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1851660</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Рисунок 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0038B310-88D2-2D23-6477-65577028A7C0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3726180" y="3962400"/>
+          <a:ext cx="1714500" cy="1714500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1083,12 +1138,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="18" x14ac:dyDescent="0.35">
-      <c r="A1" s="34" t="s">
+      <c r="A1" s="32" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
+      <c r="B1" s="32"/>
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
     </row>
     <row r="3" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3" s="33" t="s">
@@ -1737,7 +1792,7 @@
       <c r="A65" s="16">
         <v>1</v>
       </c>
-      <c r="B65" s="35" t="s">
+      <c r="B65" s="31" t="s">
         <v>154</v>
       </c>
       <c r="C65" s="3"/>
@@ -1933,10 +1988,10 @@
       <c r="E83" s="4"/>
     </row>
     <row r="84" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A84" s="31" t="s">
+      <c r="A84" s="34" t="s">
         <v>74</v>
       </c>
-      <c r="B84" s="31"/>
+      <c r="B84" s="34"/>
       <c r="C84" s="3"/>
       <c r="D84" s="3"/>
       <c r="E84" s="4"/>
@@ -2037,10 +2092,10 @@
       <c r="E93" s="4"/>
     </row>
     <row r="94" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A94" s="31" t="s">
+      <c r="A94" s="34" t="s">
         <v>83</v>
       </c>
-      <c r="B94" s="31"/>
+      <c r="B94" s="34"/>
       <c r="C94" s="3"/>
       <c r="D94" s="3"/>
       <c r="E94" s="4"/>
@@ -2141,10 +2196,10 @@
       <c r="E103" s="4"/>
     </row>
     <row r="104" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A104" s="32" t="s">
+      <c r="A104" s="35" t="s">
         <v>92</v>
       </c>
-      <c r="B104" s="32"/>
+      <c r="B104" s="35"/>
       <c r="C104" s="3"/>
       <c r="D104" s="3"/>
       <c r="E104" s="4"/>
@@ -2228,11 +2283,6 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="A33:B33"/>
     <mergeCell ref="A94:B94"/>
     <mergeCell ref="A104:B104"/>
     <mergeCell ref="A43:B43"/>
@@ -2240,9 +2290,15 @@
     <mergeCell ref="A64:B64"/>
     <mergeCell ref="A74:B74"/>
     <mergeCell ref="A84:B84"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="A33:B33"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
